--- a/results/llm_as_judge/tables/EVALUATION.xlsx
+++ b/results/llm_as_judge/tables/EVALUATION.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Reponse_Qwen_2_5</t>
+          <t>Reponse_Qwen_2_5.7B</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
